--- a/光伏配储项目/电价数据/2026/岱建站.xlsx
+++ b/光伏配储项目/电价数据/2026/岱建站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.536</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.22757</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.64115</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.9970599999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.8119400000000001</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.71113</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44021</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45596</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44051</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42261</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.45232</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38328</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40149</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42433</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41098</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38416</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41538</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42612</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42234</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41223</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44563</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.46855</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.7479199999999999</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.6027400000000001</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.5016499999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.26538</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.55377</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.5794600000000001</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.25814</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.79548</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.79606</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.4831</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.15683</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.52723</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.52442</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.79137</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.8955</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.5834900000000001</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.63863</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.6199199999999999</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.7863600000000001</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.73509</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.7921</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.03055</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.31588</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.45906</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.69849</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.15617</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.96766</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.8278099999999999</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.98193</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.16907</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.93771</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.69307</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.74089</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.41282</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.14326</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.74413</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.09529</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.19582</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.41966</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.17417</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.16075</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.11767</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.7220700000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47935</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40627</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42215</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.07038</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.95739</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.0366</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53612</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5225299999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50624</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5348099999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49785</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41031</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47237</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38786</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42095</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.54774</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7537699999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72394</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45894</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.43907</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.82882</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.97113</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.6076</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.78875</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.83217</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.7255900000000001</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.6306900000000001</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.4847</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.50606</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.61624</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.02268</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.04967</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.33191</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.98154</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.24601</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8619</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.78949</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.18571</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.00935</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.9047999999999999</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.47852</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.49422</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.5830599999999999</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47662</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.1026</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.94765</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.91251</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.93691</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.84509</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7726900000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.7920499999999999</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.53746</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.88109</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.08743</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.03885</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.8635499999999999</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.24399</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.47687</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.41614</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.48747</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.58576</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.56945</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.73086</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.0907</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.19466</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.9202899999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.65623</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.62638</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.7815800000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44072</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41756</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33348</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5154500000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.46645</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.54057</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.43229</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.43798</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41539</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43357</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44949</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39316</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.4733</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44398</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39671</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.62091</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.63497</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.7936799999999999</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.64685</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.60319</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.60323</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.46291</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.48748</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.39009</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.68953</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.90203</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.24272</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.60653</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.97382</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.30238</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8137000000000001</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.86163</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.67614</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.8071</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.95266</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.9363400000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6831</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.45121</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.38251</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.51422</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.9131</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.85446</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.9568300000000001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.50724</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.13589</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.13593</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.96113</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.90262</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.84842</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.28558</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.24998</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.1218</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.08499</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.12661</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.07958</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.02789</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.52042</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.90651</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.54059</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.90439</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.92526</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.9113300000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.00345</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.93199</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.03492</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.86538</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.6669700000000001</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.65079</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.49653</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.90313</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.58027</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.48797</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.46623</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.5180900000000001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.58002</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.5646100000000001</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46643</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.41713</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.57302</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.5427999999999999</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.6635700000000001</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.89711</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.95652</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.66411</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.0383</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.08406</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.63515</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.72177</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.99553</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.96911</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.19073</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.83778</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.8912</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.53849</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.67227</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.47681</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.43094</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.5280199999999999</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.81092</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.96125</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.79513</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.82505</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.85562</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.79369</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.75666</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.72061</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.9389299999999999</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.9899199999999999</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.60134</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.95196</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.8949</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.63707</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.8166</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.8631799999999999</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.7936599999999999</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.8877200000000001</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.96597</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.98289</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.9517899999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.9778600000000001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.59192</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.8998700000000001</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.8605499999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.81357</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.88528</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.91965</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.9156299999999999</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.88825</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.5967899999999999</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.44511</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.60463</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31132</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.56231</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.46123</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.20943</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.20485</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.24408</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.20474</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.28144</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.17288</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.21752</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.23346</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.45538</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.37359</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.17094</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.1666</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.45295</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.16739</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.28915</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.24206</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.18499</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.21039</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.20079</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.20025</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.15579</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.17318</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.18612</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.1642</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.5082</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.42526</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.42498</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.42327</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.43318</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.50139</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.43914</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.46069</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.45009</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.38255</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.30844</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.0067</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.76448</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.7930700000000001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5307999999999999</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.5141699999999999</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.22124</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.06456000000000001</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.1624</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04402</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04428</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04184</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009140000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20359</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04842</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04345</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.1503</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.05845</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04275</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.01574</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.0445</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04195</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04235</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.16075</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.0444</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04234</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.16124</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.16126</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.0498</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.1635</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.17405</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.18028</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.18056</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.18276</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.42267</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3359</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.38624</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.29085</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.25149</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.24437</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16013</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23742</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.27142</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.28874</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30041</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.6130099999999999</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.7203999999999999</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.56794</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.54139</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.59001</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.63915</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.78584</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.48369</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.46083</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.6339</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.62838</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.74053</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.50975</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.46493</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.40755</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.4041</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.14236</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.5962000000000001</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.59917</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.54584</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48017</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.66184</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79643</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.7342000000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.53989</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.66813</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.94787</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.25949</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.73787</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.27972</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.25242</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.66966</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.66771</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.2399</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.9177799999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.62352</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.23893</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.69562</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.64234</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.32549</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.7090299999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80449</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78762</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78831</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8785700000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88095</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50582</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41203</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41622</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46444</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22333</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6393</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54238</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50206</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45763</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42595</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43988</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39229</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45258</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39032</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45067</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.59496</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.58449</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6656</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.80588</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.56604</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5547799999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.53995</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.27511</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.86787</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.14218</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.11942</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.08771</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.47059</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.6385599999999999</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.47453</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.52724</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.46495</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.76855</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6635599999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.56508</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.51175</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.48202</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.80238</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.66991</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.3547</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5315</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.5435800000000001</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.42455</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.51495</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.50608</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.53206</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.5515</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.5049</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.52954</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.54338</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.49975</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.5290900000000001</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.52539</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.46337</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.5180800000000001</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.62783</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.5303300000000001</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.62022</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.5433300000000001</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.53814</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.5489700000000001</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.52884</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.5165</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.50384</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.51274</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.44593</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.46689</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45205</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41464</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39115</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35304</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9559</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47611</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40686</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.47795</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.5402400000000001</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4094</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.40716</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.57156</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.48255</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.51932</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.5985</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.70399</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.86607</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.6797799999999999</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.42097</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.79334</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.67589</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.7522000000000001</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.6878200000000001</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.54203</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.6554800000000001</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.7949299999999999</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.44033</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.42485</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.70943</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.11956</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.7203999999999999</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.5805900000000001</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.93083</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.64664</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.66084</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.52774</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.16066</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.61141</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.43752</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.48355</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.4182</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.79008</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59674</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.07255</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.73268</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.36269</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70356</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79531</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64976</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58361</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.69974</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.63218</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.77256</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.88466</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.7195</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.5403600000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.08405</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.5711000000000001</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.08968</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.37437</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.40535</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.96227</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.1448</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.7075399999999999</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.1642</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.01833</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.82698</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.80904</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.7858999999999999</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.80896</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.23491</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.05131</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.49568</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.65712</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.03214</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.5909500000000001</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.81456</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.79431</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.68149</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.7275199999999999</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.70733</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.8503999999999999</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.8696900000000001</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.70585</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.8781599999999999</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.14224</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.79443</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.7944199999999999</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.8881599999999999</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.7581100000000001</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.78038</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.11919</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.7662100000000001</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.78095</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.8524700000000001</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.72888</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.71651</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.32797</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.89512</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.48086</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.23501</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.8032999999999999</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.8103899999999999</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.64439</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3247</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43128</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.26285</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.27187</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.72165</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.66096</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.2444</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.26042</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28348</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.26541</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.54367</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.38964</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44953</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45035</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43991</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43927</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39031</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39749</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34933</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54231</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39077</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.43686</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.27849</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.56563</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2758</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27762</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.4104100000000001</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.53965</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.48636</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.48391</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.59521</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.80987</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.7594299999999999</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.6024299999999999</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.39617</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.53975</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.65688</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.7756000000000001</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.76215</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.64144</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.45198</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.41116</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.39362</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.42634</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.39459</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41863</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.49051</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.5704</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.7129500000000001</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.71363</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.70235</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.7046</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.00684</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.00759</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.63946</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.75627</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.17678</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.68321</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.16093</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.04106</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.03379</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.10116</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.8129</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.27849</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.44619</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.81016</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.77697</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.69557</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.0334</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.01647</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.04991</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.06326</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.05837</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.0355</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.05995</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.8077799999999999</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.09307</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.30663</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.17448</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.19777</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.09005</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.0978</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.10589</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.04286</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.14018</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.69112</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.75218</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.08388</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.09226</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.08615</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.69515</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.16558</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.48249</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.11579</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.25319</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.6146</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5236499999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.6499</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.13184</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.72649</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.41324</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.32399</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.42935</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.7551</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.5579</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.56238</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.56692</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.41471</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.43202</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.43366</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28281</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.40816</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.65812</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.95374</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.80863</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.64455</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.56055</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.39959</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.41544</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.42093</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.42688</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.40614</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.44197</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39289</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40288</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3493</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.43436</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.1081</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.42496</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.37823</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.39517</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56321</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.4173</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38372</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.54571</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.42014</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.42181</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40915</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65191</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83101</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47183</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41063</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.56784</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.54557</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.6295700000000001</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.17999</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.40531</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.27279</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.41901</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.26577</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.5268699999999999</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.40859</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.72138</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.67311</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.97604</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.43973</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.79272</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.26687</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.6394500000000001</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.7936</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.58475</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.82259</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.77174</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.61979</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.12644</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.69557</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.8975599999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.53487</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.00035</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.58505</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.93449</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.11448</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.88928</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42979</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41872</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37429</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.65504</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.14724</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.9503400000000001</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.75095</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41943</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.41663</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41095</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40862</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41752</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39551</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41128</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41825</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44946</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5604</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5005299999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.46171</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44267</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.1084</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.62513</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.71067</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.78482</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.5109</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.45517</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.63889</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.47343</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.51782</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.53391</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.7561599999999999</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.77125</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.8381900000000001</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.33619</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.77768</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.68201</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.42015</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.36067</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.28281</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.16059</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.8536</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.74034</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.10737</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.44601</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.44512</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.49622</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.51724</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.6381</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.90562</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.60064</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.77115</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.5841499999999999</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.78926</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.7808200000000001</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.26483</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.22419</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.92106</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.9222100000000001</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.06841</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.05541</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.41979</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.71855</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.52245</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.10536</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.20281</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.74594</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.74947</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.94014</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.13739</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.82316</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47798</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47138</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.02047</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.61695</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.48421</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45802</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43676</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.43002</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.45276</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.49577</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.46001</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.60594</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.5799500000000001</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.58147</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.86214</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.22955</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.11385</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.67391</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.7204700000000001</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.7311799999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.46677</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1.55602</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.45083</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.4396600000000001</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.47277</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.47146</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.43961</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41295</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42851</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.50356</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.48473</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.54676</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40255</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.63709</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.83373</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.52496</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.4308999999999999</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.40961</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.19229</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25493</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.18903</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.25473</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.26785</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.19976</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.24531</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.24331</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.27043</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28548</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.40894</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.52198</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.40434</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.44085</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.42638</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.41755</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.4969</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44556</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.40457</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.41583</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.44403</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35168</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.5868099999999999</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.20276</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.2592</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.24326</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.23615</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.19457</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.17872</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.2525</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.17453</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.19265</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.17267</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.21625</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.24944</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.23032</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.18494</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.17456</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.20947</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.16752</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.18863</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.17491</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.16775</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.19583</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.16661</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.17508</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.16663</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.18009</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.17391</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.1763</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.28437</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.21758</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.28019</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.63722</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.40396</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.31961</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.8331499999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.85487</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.41703</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.48764</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.40851</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.5478</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.51918</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.4179</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.41337</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.61325</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.55562</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.9125800000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.9156299999999999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.03479</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.88063</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.69923</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.9480499999999999</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.44254</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.42166</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.05959</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.46596</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.41815</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.22015</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.17888</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.45231</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.47886</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.18193</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.68967</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.5175299999999999</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.47821</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.8033899999999999</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.44105</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.61595</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.5400700000000001</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.93884</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.73494</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.73405</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.74205</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.7504999999999999</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.5529700000000001</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.7819700000000001</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.5883400000000001</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.80821</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.22753</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.22981</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.26126</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.6778</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.22798</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.32647</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.40467</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.78992</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.9331199999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.78422</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.83511</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.83247</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.14885</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.99274</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7736900000000001</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.5915499999999999</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33747</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.47987</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.63585</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.47025</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5932000000000001</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.59415</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.47197</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.41621</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.40987</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.39409</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.84404</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.70164</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.63962</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5972000000000001</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.48834</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.55912</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.51559</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.5037</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.27915</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.7720399999999999</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.89925</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.8118300000000001</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.90208</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.2513</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.24597</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.82289</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.8408099999999999</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.5949</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.45421</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.45678</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.4046</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.46269</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.45398</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.45245</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.5282</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.06933</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.69132</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.41923</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.45616</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.41819</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.42628</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.41811</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.43089</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.42171</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.43624</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.47918</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.47583</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.48086</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.44528</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.45679</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.4080299999999999</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.45601</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.48157</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.54976</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.89306</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.8455499999999999</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.5491900000000001</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.47852</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.98983</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.68869</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.5813400000000001</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.89173</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.7261799999999999</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.46164</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.46524</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.45291</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.41197</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.46372</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33911</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.43213</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.39479</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5888099999999999</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.5597000000000001</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.8291499999999999</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.06897</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.51119</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.73714</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.66755</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.7828099999999999</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.8217300000000001</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.77055</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.7432000000000001</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.77698</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.75562</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.74495</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.74812</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.16264</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.47234</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.7387100000000001</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.5144099999999999</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.74987</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.75714</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.61662</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.73898</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.6216499999999999</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.75218</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.7260599999999999</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.75452</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.03357</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.19294</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.21547</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.2629</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.32968</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.31273</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.38251</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.39496</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.37289</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.9761799999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.8688899999999999</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.8317</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.48044</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.04182</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.80483</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.89007</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.7592300000000001</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.69125</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.67837</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.68343</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.64877</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.68572</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.55027</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40182</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45847</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.5787899999999999</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.64891</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.61203</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36868</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.6838200000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39959</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.44093</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.69276</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.55141</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.70387</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.6085700000000001</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.60925</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.5242899999999999</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.61202</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.62414</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.82525</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.68171</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.82387</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.75507</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.83189</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.81467</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.8148099999999999</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.05592</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.07488</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.7916</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.50344</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.58296</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.6084400000000001</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.68537</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.66757</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.71666</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.2053</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.20741</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.52512</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.22825</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.52877</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.51041</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.54239</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.33362</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.25832</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.9051399999999999</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.88566</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.57138</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.64481</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.3215</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.32294</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.14536</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.55699</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.64765</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.62331</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.08205</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.02375</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.7644500000000001</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.29179</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.27024</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.54647</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.31342</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.31521</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.6634099999999999</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.64627</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.6329199999999999</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37507</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27081</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.59182</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.44525</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.5778099999999999</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.8671</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.6956</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.6254299999999999</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.6517999999999999</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.81845</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.83256</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.9570599999999999</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.55591</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.44093</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.25532</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.01305</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.96711</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.65799</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.46427</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16636</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.57525</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.34381</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.17809</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.6464500000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.22334</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.73092</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.64028</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.74356</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.52242</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.42828</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.83421</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.66722</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.56572</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.7605299999999999</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.61581</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.7455000000000001</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.83287</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.8888400000000001</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.74979</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.76047</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.7433099999999999</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.74195</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.7525599999999999</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.13177</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.18088</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.06614</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.08528</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.26115</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.01605</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.04469</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.81128</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.79173</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.80743</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.84682</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.8475900000000001</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.8288300000000001</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.93956</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.6161</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.5875499999999999</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.5321399999999999</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.51164</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.41616</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37848</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37537</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.30161</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.9002</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.92708</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.20152</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.75951</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.4236</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37565</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.62776</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.50207</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.5943200000000001</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.59493</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.5605800000000001</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.71327</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.27061</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.77146</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.84642</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.95043</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.9382200000000001</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.8357100000000001</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.04489</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.7930199999999999</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.45675</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.18165</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.43301</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.8153899999999999</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.52724</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.6253500000000001</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.81333</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.5918099999999999</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.44264</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.52391</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.99585</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.8104</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.5877599999999999</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.26139</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.84533</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.8156599999999999</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.35215</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.23065</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.04606</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.8937200000000001</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.86124</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.86974</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.86599</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.8903</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.8904299999999999</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.92487</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.34733</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.3918</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.49158</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.8446</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.86698</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.84666</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.8902</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.64594</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.0608</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.62276</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.60029</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.48223</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.9790399999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.63832</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.64007</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.44651</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.46936</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.47173</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.44664</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.45817</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.44369</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.40565</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40514</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.37218</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.40305</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.39774</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.7266900000000001</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.5660499999999999</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.85182</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.12981</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.80098</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.85161</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.53537</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.50936</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.40495</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.48549</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1.39934</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.95462</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.67359</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.41656</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.40739</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.3996499999999999</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.4795</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.56471</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.51259</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.68079</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.5295800000000001</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.8492000000000001</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.7308300000000001</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.7416</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.7682899999999999</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.78727</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.57924</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.55287</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.53532</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.55002</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.55668</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.57189</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.63714</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.64101</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.53437</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.63893</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.64724</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.93311</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.6728200000000001</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.5791799999999999</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.5829500000000001</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.56465</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.5283300000000001</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.52743</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.66152</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.63525</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.69247</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.56979</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.5262100000000001</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.47562</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.45706</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.4097</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38406</v>
       </c>
     </row>
   </sheetData>
